--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.13285262547325</v>
+        <v>7.334088551639403</v>
       </c>
       <c r="D2" t="n">
-        <v>36.65760600739868</v>
+        <v>5.956860976202285</v>
       </c>
       <c r="E2" t="n">
-        <v>12.65288998354584</v>
+        <v>2.056094622326199</v>
       </c>
       <c r="F2" t="n">
-        <v>6.529931444762898</v>
+        <v>1.061113859773971</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.43863259256493</v>
+        <v>11.4462777962918</v>
       </c>
       <c r="D3" t="n">
-        <v>23.59774311787288</v>
+        <v>3.834633256654343</v>
       </c>
       <c r="E3" t="n">
-        <v>12.65288998354584</v>
+        <v>2.056094622326199</v>
       </c>
       <c r="F3" t="n">
-        <v>6.529931444762898</v>
+        <v>1.061113859773971</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
